--- a/daily_matches/job_matches_2026-05-07.xlsx
+++ b/daily_matches/job_matches_2026-05-07.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, Terraform</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Software Engineer II - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, Keras, S3, EC2, Redshift, Data Lake, MLflow, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist, Summer Intern</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>JCPenney</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala</t>
+          <t>S3, Glue, Redshift, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,129 +566,129 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c8ae0c4d3ff5be</t>
+          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior .NET Engineer</t>
+          <t>Software Engineer III - Python Developer/AWS/Kafka</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navigate360</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richfield, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Scala</t>
+          <t>LangChain, RAG, S3, Kinesis, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173985f052eba684</t>
+          <t>https://www.indeed.com/viewjob?jk=d10e22d7e3fdf55b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>S3, EC2, Docker, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8a3b04afc12b14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Avalara</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+          <t>https://www.indeed.com/viewjob?jk=a33e6e37234bb097</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GPU Stack CI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Nebraska</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, EC2, Glue, CI/CD, GitHub Actions, Git, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a988d17a75a7be40</t>
+          <t>https://www.indeed.com/viewjob?jk=6b31f09685a51aa6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Centerfield</t>
+          <t>Samaritan's Purse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, Git, Python, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d5251e8c79cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=21fad0b59b48f752</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior - Data Engineer, Development</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Snowflake, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8743eff03c13f03d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc2422da51751bb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-07.xlsx
+++ b/daily_matches/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,104 +486,104 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Pinecone, Prompt Engineering</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Hugging Face, ChromaDB, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
+          <t>https://www.indeed.com/viewjob?jk=5942a6a495e31ed1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Engineer</t>
+          <t>Technical Architect - AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, Keras, S3, EC2, Redshift, Data Lake, MLflow, Kubernetes</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, S3, Athena, Redshift, Kinesis, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=c95a4d7ac3a5fbfd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JCPenney</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, ChromaDB, Prompt Engineering, Azure ML</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python Developer/AWS/Kafka</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, Kinesis, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, spaCy, NLTK, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,182 +601,1897 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10e22d7e3fdf55b</t>
+          <t>https://www.indeed.com/viewjob?jk=deed7b23c19ec4ce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, spaCy, NLTK, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a3b04afc12b14</t>
+          <t>https://www.indeed.com/viewjob?jk=9dee407d8862d52b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Data Lake, Docker, Kubernetes, CI/CD, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33e6e37234bb097</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GPU Stack CI Infrastructure Engineer</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, EC2, Glue, CI/CD, GitHub Actions, Git, R</t>
+          <t>Data Scientist, S3, EC2, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b31f09685a51aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Samaritan's Purse</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fad0b59b48f752</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Research Scientist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1c35e0e10bd4748</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64300e27d0c96342</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Databricks, PySpark</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4b2c968aa2d99a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Databricks, PySpark</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbf14c46b315c81c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PySpark, PostgreSQL, MongoDB, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PySpark, PostgreSQL, MongoDB, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=753ffd3f5a797949</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd720a9aa988f104</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bf27b58e983548e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c0701516d95b44d</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a857259169839e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Hadoop, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ba89a455c0ae677</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed1050a9bc027373</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67c0b90cb12b2824</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c961354386ea486</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Kafka</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa27b807afb310c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Kafka</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7511edab0d7ee6a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=970ab5a363158d63</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AlohaABA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Hugging Face, Docker, Kubernetes, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1eb69ff0d1aa7ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DASi LLC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Doral, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ad860d53eea84c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>data scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jabil</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, OpenCV, Power BI, Matplotlib, Seaborn, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69838743e6545aef</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=662f2287dd40e7f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Legal Practice Technology Data Scientist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Scigon</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6458330f08e51fec</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data engineer with Snowflake AND Databricks</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>KIZEN Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Data Lake, Snowflake, Databricks, Hadoop, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NTT Global Data Centers Americas, Inc.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2bc3768a23b7714</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Glue, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff25c6ca254fb585</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c719bd7f0aaf1f3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7b0beb57c6b86d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI Expert Software Engineer – Healthcare Analytics IC5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d59e68c478556131</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61a367abd4c30982</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI Support Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbeab3c76c40b9b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75cf362421846ead</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=049e7e00aa1dff1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI Agent Developer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a255f6576763c5af</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AI Systems Administrator</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2c50572a8b1a6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb3e80546b892928</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4c95148b6fab29f</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Expel</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc2422da51751bb</t>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5f0d3a3ce166b3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Machine Learning</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8276509ae935e62c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LexisNexis Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60f060de611e02f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c88fe586761562f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, Copilot, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4f53293e2e96191</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, FAISS, TensorFlow, PyTorch, XGBoost, Hadoop, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6796de3a011e234</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f599148a590a77ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a8dab729d9cab66</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c9c617e02f064b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, Prompt Engineering, CI/CD, Git, MongoDB, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b96244b2780ea0e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI Research Scientist</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52862a1be4bc66fd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-07.xlsx
+++ b/daily_matches/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Hugging Face, ChromaDB, Prompt Engineering, TensorFlow</t>
+          <t>Data Scientist, RAG, S3, EC2, Redshift, BigQuery, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5942a6a495e31ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Technical Architect - AI</t>
+          <t>Data / Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Excel Services Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, S3, Athena, Redshift, Kinesis, FastAPI, Docker</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Kinesis, CI/CD, Terraform, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95a4d7ac3a5fbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UCCU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, ChromaDB, Prompt Engineering, Azure ML</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, CI/CD, Git, Snowflake, BigQuery, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Business Systems Analyst III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, spaCy, NLTK, NoSQL</t>
+          <t>RAG, Copilot, Hugging Face, TensorFlow, PyTorch, S3, Glue, Redshift, AKS, Apache Airflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deed7b23c19ec4ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e422e74a7ad211de</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, spaCy, NLTK, NoSQL</t>
+          <t>S3, Redshift, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dee407d8862d52b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ffbea23a61e7b59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Senior AI Engineer – LLM, RAG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BrightAI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Data Lake, Docker, Kubernetes, CI/CD, Kafka, Hadoop</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, Prompt Engineering, PyTorch</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a0db29f73fa4cc9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Hume AI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Git</t>
+          <t>Machine Learning Engineer, RAG, BigQuery, FastAPI, Docker, Kubernetes, Terraform, BigQuery, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1da4b50f5449e9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Cloud Engineer Observability SRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git, NoSQL, Power BI</t>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=89e50c0beedc5b59</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Remote Senior Applied Machine Learning Engineer - Applied Machine Learning Team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git, NoSQL, Power BI</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a51735170a7e5df7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, PostgreSQL</t>
+          <t>RAG, EC2, Athena, Kubernetes, Terraform, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c35e0e10bd4748</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, PostgreSQL</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64300e27d0c96342</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Arize AI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Databricks, PySpark</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b2c968aa2d99a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1c09490828979cb6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Solutions Engineer, EMEA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Arize AI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Databricks, PySpark</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf14c46b315c81c</t>
+          <t>https://www.indeed.com/viewjob?jk=06b30612fba469be</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PySpark, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Associate, AI ML Platform Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PySpark, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=794c2024a6b827e2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Developer, Platform Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753ffd3f5a797949</t>
+          <t>https://www.indeed.com/viewjob?jk=278d913f98758715</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior AI Engineer – Enterprise Applications</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, CI/CD</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd720a9aa988f104</t>
+          <t>https://www.indeed.com/viewjob?jk=0ab157c4a19c9171</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Grid Elevated</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, CI/CD</t>
+          <t>TensorFlow, XGBoost, S3, Glue, Athena, Docker, Terraform, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bf27b58e983548e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0d3426744c1c66f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,15 +1108,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0701516d95b44d</t>
+          <t>https://www.indeed.com/viewjob?jk=139b0da12e094b86</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git</t>
+          <t>RAG, S3, Glue, Athena, Databricks, PySpark, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a857259169839e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PUMP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Hadoop, Python, R</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba89a455c0ae677</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fff93e9f1e0bbd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Sr. Data Scientist - AI Program Office -Information Technology</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1050a9bc027373</t>
+          <t>https://www.indeed.com/viewjob?jk=1cebf7f3652d14a5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git</t>
+          <t>Machine Learning Engineer, LangChain, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c0b90cb12b2824</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Databricks, Python</t>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c961354386ea486</t>
+          <t>https://www.indeed.com/viewjob?jk=52cd2825e17099d5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>2026 Intern - Applied Science/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Kafka</t>
+          <t>Machine Learning Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27b807afb310c9</t>
+          <t>https://www.indeed.com/viewjob?jk=82253e72b1006a85</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior AI Engineer, Time-Series Signal Processing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BrightAI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Kafka</t>
+          <t>AI Engineer, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7511edab0d7ee6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=77b4dc55cc53f718</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Computer Vision/AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BrightAI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
+          <t>AI Engineer, TensorFlow, PyTorch, YOLO, Docker, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=970ab5a363158d63</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1d9f281da927d5</t>
         </is>
       </c>
     </row>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AlohaABA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Hugging Face, Docker, Kubernetes, Git, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Gemini, Pinecone, BigQuery, BigQuery, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1eb69ff0d1aa7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=54bada5b32565e22</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Product Engineer, Backend</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>Arize AI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad860d53eea84c9</t>
+          <t>https://www.indeed.com/viewjob?jk=60fec9643f829a74</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Keras, OpenCV, Power BI, Matplotlib, Seaborn, Python, R</t>
+          <t>Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69838743e6545aef</t>
+          <t>https://www.indeed.com/viewjob?jk=e703958313608fde</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Data Lake, Jenkins, Terraform, Git, Databricks, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Loyola University Chicago</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662f2287dd40e7f9</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdb8466fddae134</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Legal Practice Technology Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6458330f08e51fec</t>
+          <t>https://www.indeed.com/viewjob?jk=595f48c6de986c3b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, Snowflake, Databricks, Hadoop, Python, SQL, R</t>
+          <t>RAG, Snowflake, Databricks, Hadoop, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Software Engineer III/Senior, Agent</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT Global Data Centers Americas, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, Python, R</t>
+          <t>EC2, Kubernetes, AKS, Terraform, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2bc3768a23b7714</t>
+          <t>https://www.indeed.com/viewjob?jk=36335acb76476a29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Glue, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff25c6ca254fb585</t>
+          <t>https://www.indeed.com/viewjob?jk=92483822db395dd4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>SENIOR CLOUD ENGINEER</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scripps Research</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c719bd7f0aaf1f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca3c7587af1adf3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Senior Associate, Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Redshift, CI/CD, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b0beb57c6b86d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b09594ce35df0493</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Expert Software Engineer – Healthcare Analytics IC5</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>E Tech Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, TensorFlow, PyTorch, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59e68c478556131</t>
+          <t>https://www.indeed.com/viewjob?jk=f04c26adf1bfe748</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Deployment Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Docker, Kubernetes, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,637 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a367abd4c30982</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AI Support Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbeab3c76c40b9b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>AI Intern</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75cf362421846ead</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>AI Model Deployment Administrator</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=049e7e00aa1dff1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AI Agent Developer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a255f6576763c5af</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>AI Systems Administrator</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Docker, Kubernetes, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c50572a8b1a6aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb3e80546b892928</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c95148b6fab29f</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Expel</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f0d3a3ce166b3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Machine Learning</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8276509ae935e62c</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>LexisNexis Risk Solutions</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60f060de611e02f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c88fe586761562f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>AI Intern</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, Copilot, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4f53293e2e96191</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Data Scientist, FAISS, TensorFlow, PyTorch, XGBoost, Hadoop, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6796de3a011e234</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>ML Infrastructure Architect</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f599148a590a77ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AI Model Deployment Administrator</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8dab729d9cab66</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c617e02f064b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, Prompt Engineering, CI/CD, Git, MongoDB, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b96244b2780ea0e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AI Research Scientist</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52862a1be4bc66fd</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-07.xlsx
+++ b/daily_matches/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>CLOUD SOLUTION ARCHITECT (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>RAG, Gemini, S3, EC2, Redshift, Kinesis, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+          <t>https://www.indeed.com/viewjob?jk=7cc98bb631036b24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd7a5bec45c7d32</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Docker, Kubernetes, Jenkins, Terraform, Git, Snowflake, MySQL, Python</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kikoff</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Git, Snowflake, Databricks, Tableau, Power BI, Matplotlib</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7dd0cd975d51e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Applied AI Scientist (remote)</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Claritev</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, S3, EC2, BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bff2de405a493b2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kikoff</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala</t>
+          <t>RAG, Kinesis, Docker, Kubernetes, Snowflake, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3273087d19a133</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Analyst | The Points Guy</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Envision Pharma Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22880f1a8cf37248</t>
+          <t>https://www.indeed.com/viewjob?jk=4e038a6ada252794</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Product &amp; Growth Analyst</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trust &amp; Will</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AKS, Git, Matplotlib, Seaborn, Python, SQL, R, Optimization</t>
+          <t>TensorFlow, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803697a26bd6e57d</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Future Secure AI</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>TensorFlow, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,137 +811,137 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa6451e47d9dd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior DevOps Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>MADISON GAS AND ELECTRIC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Kafka, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2d4d64ce64918d</t>
+          <t>https://www.indeed.com/viewjob?jk=03097a5374e579b4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist II - Digital Foundry</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, CI/CD, Snowflake, Redshift, Python, SQL, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Tableau, Matplotlib, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=52bd2c9c1c7458aa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Scientist II - Digital Foundry</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Tableau, Matplotlib, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77796050db72c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a685c09141a75bf4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Technology Solutions Analyst</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CEC Facilities</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>Generative AI, RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, Git, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,707 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069975d977938aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Analyst</t>
+          <t>Senior Engineer, Test and Automation (Remote, US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Minnesota</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97cf888a72ff8c87</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Motive</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Cortex, CI/CD, Terraform, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior AI Application Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EVERSANA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, LLaMA, Gemini, Mistral, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7b165a5b0bfcd5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - AI Platform</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WEX Inc.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer 4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BLOC Resources, LLC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, PyTorch, XGBoost, LightGBM, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=313e1b8a59adb9be</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Toyota North America</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cellebrite</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0638b0ba0c0b42d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Prompt Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, FastAPI, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bbec0b6280efca7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Forma</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23c7af77b42a5061</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Celigo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Git, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dca27a71071125b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Engineer II, Software</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CarMax</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a70bacf4db0c6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Associate AI/ML Engineer - AI Program</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=784b34c3e3482f38</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Core Infrastructure (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Renew home</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d16058753d4a92c8</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df37e9e9b173e536</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NextEra Energy</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Juno Beach, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e35730f3d59011</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Scientist - Sr. Consultant Level</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30e034ce9bc52142</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist - Sr. Consultant Level</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0417d30940f05a60</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Scientist - Sr. Consultant Level</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92a411a0a63f6475</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist, AI/ML – Visa Consulting and Analytics</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Copilot, Git, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f028780e38022fe1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-07.xlsx
+++ b/daily_matches/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CLOUD SOLUTION ARCHITECT (REMOTE OPPORTUNITY)</t>
+          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, EC2, Redshift, Kinesis, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, S3, Kinesis, MLflow, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc98bb631036b24</t>
+          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka</t>
+          <t>Data Scientist, S3, EC2, Athena, Redshift, Data Lake, CI/CD, Jenkins, Git, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>AI Engineer, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, spaCy, NLTK, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd7a5bec45c7d32</t>
+          <t>https://www.indeed.com/viewjob?jk=99a955f9ae240eaf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, NoSQL</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Data Lake, Docker, Kubernetes, CI/CD, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
+          <t>https://www.indeed.com/viewjob?jk=421d501481afea8c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Git, Snowflake, Databricks, Tableau, Power BI, Matplotlib</t>
+          <t>Copilot, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=783168b15946ba04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Data Scientist, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=1504b48ac82c81c8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=b817d3889c9496a8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Envision Pharma Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Kubernetes, CI/CD, Python</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PySpark, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e038a6ada252794</t>
+          <t>https://www.indeed.com/viewjob?jk=66346ef8e4a5a194</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Research Fellow - Artificial Intelligence/Machine Learning</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Amherst, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TensorFlow, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=bae29c34d0c2ccf3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TensorFlow, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
+          <t>S3, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Analyst</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MADISON GAS AND ELECTRIC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03097a5374e579b4</t>
+          <t>https://www.indeed.com/viewjob?jk=573de63d3acc764d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist II - Digital Foundry</t>
+          <t>Machine Learning Engineer II, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Tableau, Matplotlib, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bd2c9c1c7458aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5fcbbd60657eee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist II - Digital Foundry</t>
+          <t>Machine Learning Engineer II, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Tableau, Matplotlib, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a685c09141a75bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=08f26fd7516e2e24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Machine Learning Engineer II, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, Git, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=df1fe96c6fcd3552</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer, Test and Automation (Remote, US)</t>
+          <t>Machine Learning Engineer II, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, FastAPI, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cf888a72ff8c87</t>
+          <t>https://www.indeed.com/viewjob?jk=9d131f14501bd074</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer II, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, CI/CD, Terraform, Snowflake, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e35e19f51a5627</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Application Engineer</t>
+          <t>Google Cloud Data Architect – IAM Data Modernization</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Gemini, Mistral, Docker, Kubernetes, Git, Python, R</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, CI/CD, Git, BigQuery, PySpark, Hadoop, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b165a5b0bfcd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Athena, Redshift, Terraform, Git, Redshift, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=1febfbe512a25ee0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Lake, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=55829deca21e2b3e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, PyTorch, XGBoost, LightGBM, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Synapse, Data Lake, Snowflake, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313e1b8a59adb9be</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Data Analyst &amp; GenAI Specialist, Enterprise AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=49a3c5ea9cc7a4b0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cellebrite</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, R, Scala</t>
+          <t>AI Engineer, RAG, Pinecone, BigQuery, Snowflake, Databricks, BigQuery, PySpark, NoSQL, Python</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0638b0ba0c0b42d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2701305c0ed53c4c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Prompt Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, FastAPI, Python, R</t>
+          <t>RAG, Pinecone, FastAPI, CI/CD, GitHub Actions, Git, Databricks, Kafka, Power BI, Python</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbec0b6280efca7</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Architect/Systems Administrator</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Forma</t>
+          <t>Torch Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c7af77b42a5061</t>
+          <t>https://www.indeed.com/viewjob?jk=2396d9b64af7a3d3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>S3, Docker, Kubernetes, AKS, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,137 +1336,137 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=77bced32c39f343f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, S3, Kubernetes, CI/CD, Terraform, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca27a71071125b0</t>
+          <t>https://www.indeed.com/viewjob?jk=41506061e08a6c6b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer II, Software</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, S3, Kubernetes, CI/CD, Terraform, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a70bacf4db0c6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f05c8dd67fcf30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer - AI Program</t>
+          <t>Senior, Data Scientist - Membership Insights (Contact Center)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, Git, PySpark, Tableau, Matplotlib, Python, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=784b34c3e3482f38</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b33bacbe26b0ad</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer, Core Infrastructure (Remote, US)</t>
+          <t>AI Solutions Engineer, Global</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df37e9e9b173e536</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6b5e339cebc3b8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e35730f3d59011</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9914c5f9fbf980</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist - Sr. Consultant Level</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Future</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, S3, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e034ce9bc52142</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7cb4ddf4e5dcf5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist - Sr. Consultant Level</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0417d30940f05a60</t>
+          <t>https://www.indeed.com/viewjob?jk=7371b165388ef5f9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist - Sr. Consultant Level</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Plains Marketing</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Data Lake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a411a0a63f6475</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f17b29439c5823</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist, AI/ML – Visa Consulting and Analytics</t>
+          <t>Software Development Engineer III, Popeyes, US&amp;C</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Popeyes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Git, Tableau, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,112 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f028780e38022fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=847ff1b2f01d9acf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist, New College Grad - 2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e76bf863e8b0d4c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Contact Center AI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, BigQuery, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d924d62960a4362c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise | HPE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Westford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=594df5ff52132842</t>
         </is>
       </c>
     </row>
